--- a/survey_templates/045_cultural_and_entertainment_insights_survey--survey_templates.xlsx
+++ b/survey_templates/045_cultural_and_entertainment_insights_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1056,8 +1056,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'18-24'}</t>
+          <t>18-24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '18-24'}</t>
+          <t>18-24</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'25-34'}</t>
+          <t>25-34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': '25-34'}</t>
+          <t>25-34</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'35-44'}</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '35-44'}</t>
+          <t>35-44</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'45-54'}</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': '45-54'}</t>
+          <t>45-54</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'55-64'}</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '55-64'}</t>
+          <t>55-64</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'65_or_older'}</t>
+          <t>65_or_older</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': '65 or older'}</t>
+          <t>65 or older</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'print'}</t>
+          <t>print</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Print'}</t>
+          <t>Print</t>
         </is>
       </c>
     </row>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'mandarin'}</t>
+          <t>mandarin</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Mandarin'}</t>
+          <t>Mandarin</t>
         </is>
       </c>
     </row>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1374,12 +1374,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1442,12 +1442,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1459,12 +1459,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1493,12 +1493,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'In person'}</t>
+          <t>In person</t>
         </is>
       </c>
     </row>
@@ -1578,12 +1578,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1595,12 +1595,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'mobile_app'}</t>
+          <t>mobile_app</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Mobile app'}</t>
+          <t>Mobile app</t>
         </is>
       </c>
     </row>
@@ -1612,12 +1612,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'phone_call'}</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Phone call'}</t>
+          <t>Phone call</t>
         </is>
       </c>
     </row>
@@ -1629,12 +1629,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'computer'}</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Computer'}</t>
+          <t>Computer</t>
         </is>
       </c>
     </row>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'mobile'}</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Mobile'}</t>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'tablet'}</t>
+          <t>tablet</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Tablet'}</t>
+          <t>Tablet</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'ios'}</t>
+          <t>ios</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'iOS'}</t>
+          <t>iOS</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'android'}</t>
+          <t>android</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Android'}</t>
+          <t>Android</t>
         </is>
       </c>
     </row>
@@ -1714,12 +1714,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'windows'}</t>
+          <t>windows</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Windows'}</t>
+          <t>Windows</t>
         </is>
       </c>
     </row>
@@ -1731,12 +1731,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'chrome'}</t>
+          <t>chrome</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Chrome'}</t>
+          <t>Chrome</t>
         </is>
       </c>
     </row>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'safari'}</t>
+          <t>safari</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Safari'}</t>
+          <t>Safari</t>
         </is>
       </c>
     </row>
@@ -1765,12 +1765,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'firefox'}</t>
+          <t>firefox</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Firefox'}</t>
+          <t>Firefox</t>
         </is>
       </c>
     </row>
@@ -1782,12 +1782,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'macos'}</t>
+          <t>macos</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'macOS'}</t>
+          <t>macOS</t>
         </is>
       </c>
     </row>
@@ -1799,12 +1799,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'windows'}</t>
+          <t>windows</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Windows'}</t>
+          <t>Windows</t>
         </is>
       </c>
     </row>
@@ -1816,12 +1816,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'linux'}</t>
+          <t>linux</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Linux'}</t>
+          <t>Linux</t>
         </is>
       </c>
     </row>
